--- a/JsonConverter/ExcelFiles/Wave.xlsx
+++ b/JsonConverter/ExcelFiles/Wave.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC598D71-A050-4FD1-93BE-E05B89839D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB3516A-7A6F-494E-81AD-8CBB87CDEBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -129,13 +129,33 @@
   <si>
     <t>wave3_03</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave4_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave4_02</t>
+  </si>
+  <si>
+    <t>wave4_03</t>
+  </si>
+  <si>
+    <t>wave5_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave5_02</t>
+  </si>
+  <si>
+    <t>wave5_03</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -161,13 +181,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -278,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -299,18 +312,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -870,8 +880,12 @@
       <c r="N12" s="4"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -886,8 +900,12 @@
       <c r="N13" s="4"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="A14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="5">
+        <v>2</v>
+      </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -902,8 +920,12 @@
       <c r="N14" s="4"/>
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+      <c r="A15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="5">
+        <v>3</v>
+      </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -918,8 +940,12 @@
       <c r="N15" s="4"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
+      <c r="A16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -930,8 +956,12 @@
       <c r="J16" s="9"/>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
+      <c r="A17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="5">
+        <v>2</v>
+      </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -942,8 +972,12 @@
       <c r="J17" s="9"/>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
+      <c r="A18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="5">
+        <v>3</v>
+      </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>

--- a/JsonConverter/ExcelFiles/Wave.xlsx
+++ b/JsonConverter/ExcelFiles/Wave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB3516A-7A6F-494E-81AD-8CBB87CDEBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C21291A-82CF-496C-9669-FAE87E679B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -719,16 +719,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
       </c>
       <c r="E7" s="1">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F7" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>

--- a/JsonConverter/ExcelFiles/Wave.xlsx
+++ b/JsonConverter/ExcelFiles/Wave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C21291A-82CF-496C-9669-FAE87E679B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26345717-0288-46DB-A2A4-7FBF68434A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="3105" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -660,7 +660,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
@@ -688,7 +688,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -743,8 +743,8 @@
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="6">
-        <v>2</v>
+      <c r="B8" s="5">
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -771,8 +771,8 @@
       <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="6">
-        <v>3</v>
+      <c r="B9" s="5">
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
@@ -799,7 +799,7 @@
       <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="3">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -827,8 +827,8 @@
       <c r="A11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="1">
-        <v>2</v>
+      <c r="B11" s="5">
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>14</v>
@@ -855,8 +855,8 @@
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="6">
-        <v>3</v>
+      <c r="B12" s="5">
+        <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>14</v>
@@ -904,7 +904,7 @@
         <v>27</v>
       </c>
       <c r="B14" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -924,7 +924,7 @@
         <v>28</v>
       </c>
       <c r="B15" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -960,7 +960,7 @@
         <v>30</v>
       </c>
       <c r="B17" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -976,7 +976,7 @@
         <v>31</v>
       </c>
       <c r="B18" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>

--- a/JsonConverter/ExcelFiles/Wave.xlsx
+++ b/JsonConverter/ExcelFiles/Wave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26345717-0288-46DB-A2A4-7FBF68434A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D8AADB-68B5-4784-B638-9AEEBF6D0F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3105" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
   <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -138,17 +138,45 @@
     <t>wave4_02</t>
   </si>
   <si>
+    <t>wave5_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave5_02</t>
+  </si>
+  <si>
+    <t>wave5_03</t>
+  </si>
+  <si>
     <t>wave4_03</t>
-  </si>
-  <si>
-    <t>wave5_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave5_02</t>
-  </si>
-  <si>
-    <t>wave5_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave4_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave4_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave5_04</t>
+  </si>
+  <si>
+    <t>wave5_06</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave5_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave5_07</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave5_08</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -205,7 +233,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -227,12 +255,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor rgb="FFD86DCD"/>
       </patternFill>
     </fill>
@@ -246,6 +268,96 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-4.9989318521683403E-2"/>
+        <bgColor rgb="FF4D93D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-4.9989318521683403E-2"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FF4D93D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FF4D93D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor rgb="FF4D93D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF4D93D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -291,7 +403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -304,23 +416,65 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -576,8 +730,8 @@
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="9"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" s="1" t="s">
@@ -601,479 +755,611 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="9"/>
-    </row>
-    <row r="3" spans="1:14" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:14" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="11"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="13">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="1">
-        <v>5</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="D4" s="14">
+        <v>3</v>
+      </c>
+      <c r="E4" s="15">
+        <v>1</v>
+      </c>
+      <c r="F4" s="14">
         <v>0</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="9"/>
+      <c r="J4" s="7"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="16">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="14">
         <v>3</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="14">
         <v>0.5</v>
       </c>
-      <c r="F5" s="1">
-        <v>4</v>
+      <c r="F5" s="14">
+        <v>5</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="9"/>
+      <c r="J5" s="7"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="16">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="14">
         <v>2</v>
       </c>
-      <c r="E6" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="F6" s="1">
-        <v>6</v>
+      <c r="E6" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="14">
+        <v>8</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="9"/>
+      <c r="J6" s="7"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="17">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="18">
         <v>5</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="18">
         <v>0.5</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="18">
         <v>0</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="9"/>
+      <c r="J7" s="7"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="19">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="18">
         <v>5</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="18">
         <v>0.25</v>
       </c>
-      <c r="F8" s="1">
-        <v>6</v>
+      <c r="F8" s="18">
+        <v>3</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="9"/>
+      <c r="J8" s="7"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="19">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="18">
         <v>5</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="18">
         <v>0.25</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="18">
         <v>6</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="9"/>
+      <c r="J9" s="7"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="20">
         <v>1</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="1">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="D10" s="21">
+        <v>8</v>
+      </c>
+      <c r="E10" s="21">
         <v>0.25</v>
       </c>
-      <c r="F10" s="1">
-        <v>6</v>
+      <c r="F10" s="21">
+        <v>0</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="9"/>
+      <c r="J10" s="7"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="22">
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="21">
         <v>5</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="21">
         <v>0.25</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="21">
         <v>6</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="9"/>
+      <c r="J11" s="7"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="22">
         <v>2</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="21">
         <v>5</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="21">
         <v>0.25</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="21">
         <v>6</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="9"/>
+      <c r="J12" s="7"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="23">
         <v>1</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="C13" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="24">
+        <v>5</v>
+      </c>
+      <c r="E13" s="24">
+        <v>0.25</v>
+      </c>
+      <c r="F13" s="24">
+        <v>0</v>
+      </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="9"/>
+      <c r="J13" s="7"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="25">
         <v>1</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="C14" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="24">
+        <v>5</v>
+      </c>
+      <c r="E14" s="24">
+        <v>0.25</v>
+      </c>
+      <c r="F14" s="24">
+        <v>2</v>
+      </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="9"/>
+      <c r="J14" s="7"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="5">
+      <c r="A15" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="25">
+        <v>2</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="24">
+        <v>3</v>
+      </c>
+      <c r="E15" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="24">
         <v>1</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="9"/>
+      <c r="J15" s="7"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="3">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="A16" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="24">
+        <v>2</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="24">
+        <v>3</v>
+      </c>
+      <c r="E16" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="24">
+        <v>4</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="9"/>
+      <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="5">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+      <c r="A17" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="24">
+        <v>3</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="24">
+        <v>2</v>
+      </c>
+      <c r="E17" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="24">
+        <v>10</v>
+      </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="9"/>
+      <c r="J17" s="7"/>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="5">
+      <c r="A18" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="26">
         <v>1</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="C18" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="27">
+        <v>5</v>
+      </c>
+      <c r="E18" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="F18" s="27">
+        <v>0</v>
+      </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="9"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="A19" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="28">
+        <v>1</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="27">
+        <v>5</v>
+      </c>
+      <c r="E19" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="F19" s="27">
+        <v>2</v>
+      </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="9"/>
+      <c r="J19" s="7"/>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="A20" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="28">
+        <v>1</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="27">
+        <v>3</v>
+      </c>
+      <c r="E20" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="F20" s="27">
+        <v>4</v>
+      </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="9"/>
+      <c r="J20" s="7"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+      <c r="A21" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="28">
+        <v>2</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="27">
+        <v>3</v>
+      </c>
+      <c r="E21" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="27">
+        <v>4</v>
+      </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="9"/>
+      <c r="J21" s="7"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+      <c r="A22" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="28">
+        <v>2</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="27">
+        <v>2</v>
+      </c>
+      <c r="E22" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="27">
+        <v>6</v>
+      </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="9"/>
+      <c r="J22" s="7"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="A23" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="27">
+        <v>3</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="27">
+        <v>2</v>
+      </c>
+      <c r="E23" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="27">
+        <v>8</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="9"/>
+      <c r="J23" s="7"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="A24" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="28">
+        <v>3</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="27">
+        <v>2</v>
+      </c>
+      <c r="E24" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="F24" s="27">
+        <v>9</v>
+      </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="9"/>
+      <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="A25" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="28">
+        <v>4</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="27">
+        <v>1</v>
+      </c>
+      <c r="E25" s="27">
+        <v>0</v>
+      </c>
+      <c r="F25" s="27">
+        <v>10</v>
+      </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="9"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -1081,11 +1367,11 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="9"/>
+      <c r="J26" s="7"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1093,11 +1379,11 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="9"/>
+      <c r="J27" s="7"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -1105,11 +1391,11 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="9"/>
+      <c r="J28" s="7"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -1117,11 +1403,11 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="9"/>
+      <c r="J29" s="7"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -1129,11 +1415,11 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="9"/>
+      <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -1141,7 +1427,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="9"/>
+      <c r="J31" s="7"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="3"/>
@@ -1153,19 +1439,19 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="9"/>
+      <c r="J32" s="7"/>
     </row>
     <row r="33" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
     </row>
     <row r="34" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
     </row>
     <row r="35" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
     </row>
     <row r="36" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:2" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Wave.xlsx
+++ b/JsonConverter/ExcelFiles/Wave.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D8AADB-68B5-4784-B638-9AEEBF6D0F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFE480F-6095-4154-894E-2ABA908EDD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
   <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -176,6 +176,18 @@
   </si>
   <si>
     <t>wave5_08</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_05</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -929,10 +941,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="D9" s="18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" s="18">
         <v>0.25</v>
@@ -985,10 +997,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D11" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" s="21">
         <v>0.25</v>
@@ -1013,7 +1025,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D12" s="21">
         <v>5</v>
